--- a/DS_HS2026_LNW_I_Examples/AP02/smartphone_data.xlsx
+++ b/DS_HS2026_LNW_I_Examples/AP02/smartphone_data.xlsx
@@ -870,7 +870,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Antwort von GET /v1/reviews?category=smartphones</t>
+          <t>PhoneMarkt Reviews API (fiktiv): Antwort von GET /v1/reviews?category=smartphones, abgerufen am 15.09.2026</t>
         </is>
       </c>
     </row>

--- a/DS_HS2026_LNW_I_Examples/AP02/smartphone_data.xlsx
+++ b/DS_HS2026_LNW_I_Examples/AP02/smartphone_data.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Description" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Data Sources" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Description" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data Sources" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/DS_HS2026_LNW_I_Examples/AP02/smartphone_data.xlsx
+++ b/DS_HS2026_LNW_I_Examples/AP02/smartphone_data.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Description" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data Sources" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Description" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Data Sources" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
